--- a/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
+++ b/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
@@ -3776,38 +3776,30 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>10032000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>22800</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K51" s="5" t="n">
+        <v>10032000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>22800</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3816,7 +3808,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23315,7 +23307,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23325,7 +23317,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23745,12 +23737,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
-招标单位
--
-(在售)</t>
+$1003万
+$22,800/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">

--- a/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
+++ b/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -10665,14 +10665,14 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
         <v>9760000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>22182</v>
+        <v>22232</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>9760000</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>22182</v>
+        <v>22232</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -24689,10 +24689,10 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 440呎 (2房)
+          <t>A | 439呎 (2房)
 $976万
-$22,182/呎
-(26年-08月-18日)</t>
+$22,232/呎
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
+++ b/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
@@ -4962,38 +4962,30 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>10318000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>21631</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K70" s="5" t="n">
+        <v>10318000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>21631</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5002,7 +4994,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23307,7 +23299,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23317,7 +23309,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23951,12 +23943,12 @@
 (26年-01月-08日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
+$1032万
+$21,631/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">

--- a/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
+++ b/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3781,14 +3781,14 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
         <v>10032000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>22800</v>
+        <v>22852</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>10032000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>22800</v>
+        <v>22852</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -23731,10 +23731,10 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 440呎 (2房)
+          <t>A | 439呎 (2房)
 $1003万
-$22,800/呎
-(26年-09月-05日)</t>
+$22,852/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">

--- a/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
+++ b/九龙-启德-Double Coast I/Double Coast I_销控明细表.xlsx
@@ -3582,38 +3582,30 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>10369000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>21738</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K48" s="5" t="n">
+        <v>10369000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>21738</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3614,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23291,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23309,7 +23301,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23753,12 +23745,12 @@
 (26年-01月-13日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
+$1037万
+$21,738/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
